--- a/data/output/evaluasi_32.xlsx
+++ b/data/output/evaluasi_32.xlsx
@@ -8,16 +8,33 @@
   </bookViews>
   <sheets>
     <sheet name="3200" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="3277" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3279" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="3201" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="3214" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="3217" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="3213" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="3218" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="3274" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="3276" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="3207" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="3203" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3204" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3215" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3205" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3209" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="3210" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="3211" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="3212" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="3213" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="3275" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="3278" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="3206" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="3208" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="3216" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="3217" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="3202" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="3207" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="3214" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="3218" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="3271" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="3272" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="3274" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="3276" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="3277" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="3279" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="3201" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="3273" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,20 +498,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-21.84380730263368</v>
+        <v>6.760356617525652</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25</t>
+          <t>adhb_pi_q3-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -509,20 +526,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-40.93740048431223</v>
+        <v>-22.31751951198351</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q2-25</t>
+          <t>adhb_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -541,16 +558,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-9.109216334603829</v>
+        <v>-44.24474861892644</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q2-25</t>
+          <t>adhb_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -565,20 +582,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7.654144158989055</v>
+        <v>-37.67654770595781</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>distribusi_net_ekspor_q1-25 vs distribusi_net_ekspor_q1-25.1</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -593,20 +610,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6.884507279328478</v>
+        <v>11.55475679294221</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>distribusi_net_ekspor_q2-25 vs distribusi_net_ekspor_q2-25.1</t>
+          <t>adhk_pi_q3-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -621,20 +638,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9545367108068707</v>
+        <v>-11.32104139140933</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>q-to-q_pkrt_q1-25 vs q-to-q_pkrt_q1-25.1</t>
+          <t>adhk_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -649,20 +666,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.863261008419268</v>
+        <v>-8.069836448852133</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+          <t>adhk_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -677,20 +694,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.863261008419268</v>
+        <v>2.355301248643836</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+          <t>q-to-q_pkrt_q2-25 vs q-to-q_pkrt_q2-25.1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -709,16 +726,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.818464093641278</v>
+        <v>3.447242083665483</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+          <t>q-to-q_pklnprt_q1-25 vs q-to-q_pklnprt_q1-25.1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -733,20 +750,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.6706538586710716</v>
+        <v>-41.21535593487388</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -761,20 +778,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.373442796385376</v>
+        <v>19.18375171103516</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25 vs implisit_y-on-y_pkp_q1-25.1</t>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -789,20 +806,496 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.168979519051613</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>q2-25</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2.916537283019923</v>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D14" t="n">
+        <v>3.394258060881988</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q2-25 vs y-on-y_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>32</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3.793604096561701</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25 vs y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>32</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5.247098048427431</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q2-25 vs y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>32</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2.266106752116267</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>32</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3.198635477803279</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>32</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4.65038808531836</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>32</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3.818536755738907</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q2-25 vs c-to-c_pkrt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>32</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3.81024443562176</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>c-to-c_pkrt_q3-25 vs c-to-c_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>32</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5.101098338781964</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q2-25 vs c-to-c_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>32</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2.266106752116267</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>32</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2.273753413670313</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q2-25 vs implisit_q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>32</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.8207979903365793</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>32</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3.490137350157135</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q1-25 vs implisit_y-on-y_pdrb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>32</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2.96318151349094</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q2-25 vs implisit_y-on-y_pdrb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>32</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3.284574821343146</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25 vs implisit_y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>32</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3.249124892499414</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>32</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2.555779969343331</v>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>implisit_y-on-y_pmtb_q2-25 vs implisit_y-on-y_pmtb_q2-25.1</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -817,7 +1310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -854,29 +1347,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3276</v>
+        <v>3213</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Depok</t>
+          <t>Kabupaten Subang</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.177473223942665</v>
+        <v>-0.2276617207544432</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3213</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Subang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.808346487892582</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -891,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -928,6 +1449,1168 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>3275</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Bekasi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.4597609576040536</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3275</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Bekasi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10.99876561135535</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3275</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Bekasi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.1042269746699088</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3278</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.336346138515738</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3278</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.007477222374830628</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3278</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6.817907725753777</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3278</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.5726836679774322</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3278</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.01227868127437515</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3206</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-13.3854209453658</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3206</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2200178655002935</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3206</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.52372937501559</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3206</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.689525742461706</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3206</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>9.748942521220414</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3206</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.44934753614481</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3206</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tasikmalaya</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.143990177067438</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3208</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuningan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.7855784356657535</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3208</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuningan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.740089590912273</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3208</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuningan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9.313777761186655</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3208</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuningan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.755633660895612</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3208</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuningan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-6.822966255331677</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3208</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuningan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9.451373704521684</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3208</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuningan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.27456685314633</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3216</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bekasi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-17.77014117688767</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3216</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bekasi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.926258664105696</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3216</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bekasi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-22.52377774977435</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3216</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bekasi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-11.49358062301036</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3217</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung Barat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1234316188151004</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3217</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung Barat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.006427543997984713</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3202</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukabumi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>33.87283837577819</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3202</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Sukabumi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>12.16236521017714</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>3207</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -937,20 +2620,206 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.01817089420220034</v>
+        <v>9.37667916502804</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3207</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Ciamis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6827288026525584</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3214</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Purwakarta</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>23.00198717372454</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3214</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Purwakarta</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.3383654264878201</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3214</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Purwakarta</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.415787521836904</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3214</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Purwakarta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.028436081313141</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -965,6 +2834,964 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>20182.43005125321</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>adhb_pi_q2-25_ril vs adhb_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.088300189301476</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5.926931289689896</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.911846577823149</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.00463803396905011</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.7254881181099965</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3203</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Cianjur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-3.914898451798538</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3218</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangandaran</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.6104328231900513</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3218</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangandaran</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.41817600488882</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3218</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangandaran</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9.438069566357738</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3218</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangandaran</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.816278407432481</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3218</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangandaran</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.476728624957434</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3218</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pangandaran</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.342410156294836</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3271</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.5855437187388388</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3271</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.914345779264051</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3271</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.499141245190078</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3271</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Bogor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.781343097605853</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3272</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.24899579872696</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3272</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10.26874139921831</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3272</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10.61851901020484</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3272</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Sukabumi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8.87701474586712</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3274</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.5092401193490627</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3274</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1935176448619954</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3274</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9.373607099681172</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3274</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.115526800095182</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3274</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Cirebon</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7.931594579386764</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1002,6 +3829,136 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>3276</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Depok</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.614740218998233</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3276</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Depok</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11.40994355246121</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3276</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Depok</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7.041698374275426</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>3277</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1011,20 +3968,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4161402879692679</v>
+        <v>-3.786829491067704</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1039,20 +3996,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4161402879692679</v>
+        <v>0.8386500233297109</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>y-on-y_pkrt_q3-25_prov vs y-on-y_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1067,20 +4024,522 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01645711892398648</v>
+        <v>-2.013048451399012</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3277</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Cimahi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.255990348792638</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3277</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Cimahi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.07916806632386561</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3277</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Cimahi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.689557584276961</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3279</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Banjar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-6.468095628269064</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3279</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Banjar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.53176284185717</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3279</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Banjar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-4.868833353613168</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3279</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Banjar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-18.6101150920234</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3279</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Banjar</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-7.308612394414911</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3279</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Banjar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.27536272808257</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3279</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Banjar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.01831026737711577</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3201</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bogor</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>9.438866604546272</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3201</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bogor</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.207401032233192</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3273</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Bandung</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.874755730481091</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1095,7 +4554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,11 +4591,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3279</v>
+        <v>3204</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Banjar</t>
+          <t>Kabupaten Bandung</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1145,16 +4604,324 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.006860681881685682</v>
+        <v>-37.93564887700347</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pdrb_q1-25_ril vs implisit_q-to-q_pdrb_q1-25_rev</t>
+          <t>q-to-q_pkp_q1-25_ril vs q-to-q_pkp_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>27.17570510477007</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25_ril vs q-to-q_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9.67333316889269</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.267926885774057</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25_ril vs y-on-y_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>9.67333316889269</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7.16274207430738</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25_ril vs c-to-c_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.08040627602824386</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1052644186507918</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q2-25_ril vs implisit_y-on-y_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1839796161975186</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pkp_q2-25_ril vs sog_y-on-y_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-6.921980063905322</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7.058067193237356</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3204</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Bandung</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.261060365836861</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1169,7 +4936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1206,29 +4973,253 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3201</v>
+        <v>3215</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bogor</t>
+          <t>Kabupaten Karawang</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.0004174445714246054</v>
+        <v>-0.03617586752371801</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>implisit_q-to-q_pmtb_q2-25_ril vs implisit_q-to-q_pmtb_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3215</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Karawang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>30.58253088051065</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3215</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Karawang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6.572190127903744</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3215</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Karawang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8.455938235271661</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3215</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Karawang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.65328651575657</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3215</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Karawang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.37754329279798</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3215</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Karawang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.95322762231898</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3215</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Karawang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.05038808724225356</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3215</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Karawang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.21354186486554</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1243,7 +5234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1280,29 +5271,141 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3214</v>
+        <v>3205</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Purwakarta</t>
+          <t>Kabupaten Garut</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.6117394953906906</v>
+        <v>-0.472391825760201</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3205</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Garut</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.4256268689413948</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3205</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Garut</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9.263182774928417</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3205</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Garut</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.08179486875515531</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3205</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Garut</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7.741745846132322</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1317,7 +5420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1354,57 +5457,225 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3217</v>
+        <v>3209</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bandung Barat</t>
+          <t>Kabupaten Cirebon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-3.049925289660992</v>
+        <v>-0.5729201868745931</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3217</v>
+        <v>3209</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Bandung Barat</t>
+          <t>Kabupaten Cirebon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.408943570198178</v>
+        <v>13.72911138267157</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3209</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Cirebon</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4981256365028611</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3209</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Cirebon</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8.852066609136772</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3209</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Cirebon</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3300485614224164</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3209</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Cirebon</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.4973752837873022</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3209</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Cirebon</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.0652387030357</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_q3-25_prov vs implisit_y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3209</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Cirebon</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.436589124121408</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q3-25_prov vs implisit_y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1419,7 +5690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1456,57 +5727,85 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3213</v>
+        <v>3210</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Subang</t>
+          <t>Kabupaten Majalengka</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.963167898436096</v>
+        <v>-0.1459455410825343</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3213</v>
+        <v>3210</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Subang</t>
+          <t>Kabupaten Majalengka</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.01633708357437653</v>
+        <v>-3.538374021470124</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3210</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Majalengka</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.9503917515377177</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1521,7 +5820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1558,57 +5857,141 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3218</v>
+        <v>3211</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Pangandaran</t>
+          <t>Kabupaten Sumedang</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1263167084886505</v>
+        <v>-0.6143343634099203</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3218</v>
+        <v>3211</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Pangandaran</t>
+          <t>Kabupaten Sumedang</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.203981116013866</v>
+        <v>1.196977601194021</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3211</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumedang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>16.91770884532286</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3211</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumedang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.9439810227763135</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3211</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Sumedang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6.048035734568403</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1623,7 +6006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1660,29 +6043,141 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3274</v>
+        <v>3212</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Cirebon</t>
+          <t>Kabupaten Indramayu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.009081321310606459</v>
+        <v>-2.742495482809532</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3212</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Indramayu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>18.68514896245863</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3212</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Indramayu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.140036534305179</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3212</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Indramayu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.824992572355228</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3212</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Indramayu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.340343497917461</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_32.xlsx
+++ b/data/output/evaluasi_32.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
